--- a/leaudio/autopts_report/report_2024_12_21_17_18_46.xlsx
+++ b/leaudio/autopts_report/report_2024_12_21_17_18_46.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="2901">
   <si>
-    <t>AutoPTS Report: 2024-12-22 18:51</t>
+    <t>AutoPTS Report: 2024-12-22 18:57</t>
   </si>
   <si>
     <t>Test Case</t>

--- a/leaudio/autopts_report/report_2024_12_21_17_18_46.xlsx
+++ b/leaudio/autopts_report/report_2024_12_21_17_18_46.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="2901">
   <si>
-    <t>AutoPTS Report: 2024-12-22 18:57</t>
+    <t>AutoPTS Report: 2024-12-22 19:03</t>
   </si>
   <si>
     <t>Test Case</t>
